--- a/AAII_Financials/Yearly/ANNA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ANNA_YR_FIN.xlsx
@@ -973,10 +973,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>22000</v>
+        <v>22100</v>
       </c>
       <c r="E17" s="3">
-        <v>7400</v>
+        <v>7600</v>
       </c>
       <c r="F17" s="3">
         <v>5600</v>
@@ -1006,10 +1006,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>3000</v>
+        <v>2900</v>
       </c>
       <c r="E18" s="3">
-        <v>-6000</v>
+        <v>-6200</v>
       </c>
       <c r="F18" s="3">
         <v>-5600</v>
@@ -1054,10 +1054,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="F20" s="3">
         <v>-600</v>
@@ -1450,10 +1450,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F32" s="3">
         <v>600</v>
